--- a/Chadwicks_FULL_INVOICES_TEST_NO_MATERIAL_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
+++ b/Chadwicks_FULL_INVOICES_TEST_NO_MATERIAL_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
@@ -28,9 +28,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -551,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -620,17 +619,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>POLYISO UNDERFLOOR INSULAT 1200X2400X100MM</t>
+          <t>CARRIAGE - DELIVERY CHARGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SHEET</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -639,35 +638,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56.48</v>
+        <v>20.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>55.48</v>
+        <v>5.33</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>55.48</v>
+        <v>0.3553333333333333</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX236219</t>
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>46281.4403702179</v>
+        <v>46281.54438446146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CONCRETE SCREW TORX 30 7.5X62 100/BOX</t>
+          <t>BLUE DOLPHIN ROUGH SURFACE EXTERIOR TAPE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -681,32 +680,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H3" s="6" t="n"/>
+        <v>7.04</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0.3669902912621359</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX236219</t>
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>46281.44037021817</v>
+        <v>46281.54438446133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>46923</t>
+          <t>41318</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUP SQUARE BOLT &amp; NUT 10X130</t>
+          <t>BAUMIT N 155 HAMMER IN FIXINGS (BOX OF 100)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -715,32 +722,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H4" s="6" t="n"/>
+        <v>26.03</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.04706355591311343</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX236219</t>
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>46281.44037021828</v>
+        <v>46281.54438446119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>22565</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MUDGUARD WASHER M6 X 30MM</t>
+          <t>BAUMIT STAR CONTACT BONDING MORTAR 25KG WHITE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -749,27 +764,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H5" s="6" t="n"/>
+        <v>19.81</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.04759386567953464</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX236219</t>
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>46281.44037021837</v>
+        <v>46281.54438446102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>414122</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SDS+ MASONRY DRILL BIT 5.0 X 160MM 4 CUTTER</t>
+          <t>BAUMIT PVC ANGLE (CORNER) BEAD WITH MESH 2.5M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -783,40 +806,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.09</v>
+        <v>3.24</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.09</v>
+        <v>0.14</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2.09</v>
+        <v>0.04516129032258065</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX236219</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46281.44037021845</v>
+        <v>46281.54438446047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>414138</t>
+          <t>96335</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SDS+ MASONRY DRILL BIT 12.0 X 450MM 4 CUTTER</t>
+          <t>CARBERY ATTIC TANK JACKET (PACK 10) AT44. AT58. AT45R, AT60R, AT80R</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>PACK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -825,35 +848,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>14.21</v>
+        <v>424.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX236186</t>
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46281.44037021854</v>
+        <v>46281.54438325853</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>442612</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MASONMATE THROUGHBOLT M10 X 65MM OPT7 100S</t>
+          <t>RONSEAL BIG HOLE 1.2L FILLER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -867,27 +881,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.58</v>
+        <v>13.48</v>
       </c>
       <c r="H8" s="6" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX235984</t>
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>46281.44037021863</v>
+        <v>46281.54438180056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>442616</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MASONMATE THROUGHBOLT M10 X 120MM OPT7 50S</t>
+          <t>EVO-SEAL SYSTEM G GUN APPLIED EXPAND FOAM 750ML</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -901,32 +915,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.89</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H9" s="6" t="n"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CA313212</t>
+          <t>SX235981</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>46281.4403702187</v>
+        <v>46281.54438085141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>22501</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KORE EPS70 EWI GREY 100 X 1200 X 600MM 4.32M2/BALE EXTERNAL WALL INSULATION</t>
+          <t>BAUMIT STARTEX MESH ROLL 4MM X 4MM 50M2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BALE</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -935,32 +949,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="H10" s="6" t="n"/>
+        <v>67.75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.04681705809641533</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SX235828</t>
+          <t>SX235981</t>
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>46281.44045687889</v>
+        <v>46281.54438085121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>214501</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADJUSTABLE &amp; LINKING PRO WORK PLATFORM</t>
+          <t>EXT WALL INS PVC WINDOW PROFILE BASIC 2.4M LS-US8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -969,35 +991,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>142.27</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>141.27</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>141.27</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CA313706</t>
+          <t>SX235981</t>
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>46281.44037319587</v>
+        <v>46281.54438085092</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29745</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARC FOAM GUN</t>
+          <t>REISSER R2 C/W WERA PZ2 BIT 4.5 X 80MM 450/TUB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1011,32 +1025,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33.46</v>
+        <v>23.37</v>
       </c>
       <c r="H12" s="6" t="n"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CA313706</t>
+          <t>SX235946</t>
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>46281.44037319559</v>
+        <v>46281.54437980019</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+          <t>4.8M 50X22 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SHEET</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1045,40 +1059,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="F13" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0.0581081081081081</v>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SX235828</t>
+          <t>CA316115</t>
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>46281.44045687928</v>
+        <v>46281.54437880626</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>83025</t>
+          <t>449886</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3/4" IRISH TECTITE STRAIGHT COUPLING</t>
+          <t>NITRILE DIPPED GLOVES XL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1087,32 +1093,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="H14" s="6" t="n"/>
+        <v>3.11</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SX235440</t>
+          <t>CA316114</t>
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>46281.44044909765</v>
+        <v>46281.54437780003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TRACER LASER MEASURE ALM100 ALM100 TRACER</t>
+          <t>4.2M 50X22 WHITE DEAL PAO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1121,35 +1126,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>88.62</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>87.62</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>87.62</v>
-      </c>
+        <v>3.15</v>
+      </c>
+      <c r="H15" s="6" t="n"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LY203947</t>
+          <t>CA316114</t>
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>46281.44037534914</v>
+        <v>46281.54437779972</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SEWER GULLY GRID 160 X 160MM</t>
+          <t>BAUMIT SILIKONTOP K1.5MM COLOUR TINT 25KG 40 NO. TINTED TO 0198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1163,40 +1160,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.51</v>
+        <v>88.37</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51</v>
+        <v>3.97</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4.51</v>
+        <v>0.04703791469194313</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LY203947</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>46281.44037534983</v>
+          <t>SX235895</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>46281.44045780093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52238</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KRINO 10X210MM SDS BIT DISPLAY PACK</t>
+          <t>KORE EPS70 EWI GREY 100 X 1200 X 600MM 4.32M2/BALE EXTERNAL WALL INSULATION</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BALE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1205,32 +1202,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.8</v>
+        <v>41.95</v>
       </c>
       <c r="H17" s="6" t="n"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>N751006</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>46281.44037641572</v>
+          <t>SX235828</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>46281.440456875</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEWALT SDS HAMMER BODY ONLY 18V DWDCH273N-XJ</t>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SHEET</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1239,32 +1236,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>227.62</v>
-      </c>
-      <c r="H18" s="6" t="n"/>
+        <v>15.66</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0581081081081081</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>N751006</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>46281.44037641602</v>
+          <t>SX235828</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>46281.440456875</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52239</t>
+          <t>51040</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KRINO 12X210MM SDS BIT DISPLAY PACK</t>
+          <t>STANLEY 5 X 18MM SAFETY BLADES 211301</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1273,27 +1278,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.8</v>
+        <v>5.08</v>
       </c>
       <c r="H19" s="6" t="n"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>N751006</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>46281.44037641613</v>
+          <t>SX235828</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>46281.440456875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>260739</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>THERMOPLUS 500 X 600MM K2 RADIATOR 3059</t>
+          <t>PLUMB CENTRE SOIL BRANCH 110MM D/S BLACK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1307,27 +1312,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>12.13</v>
       </c>
       <c r="H20" s="6" t="n"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SN341278</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>46281.44038170587</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>455158</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MASONMATE M10 X 100 HEX SCREWBOLT OPT1 ZP 25S</t>
+          <t>1/2" CXC ISOLATING VALVE STRAIGHT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1341,32 +1346,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.35</v>
+        <v>3.22</v>
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SN341278</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>46281.44038170621</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>83985</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 1" 351</t>
+          <t>4MT X 1 1/4" WHITE WASTE PIPE LENGTH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1375,27 +1380,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11.18</v>
+        <v>10.66</v>
       </c>
       <c r="H22" s="6" t="n"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SN341278</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>46281.44038170633</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>89604</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EXT WALL INS PVC WINDOW PROFILE BASIC 2.4M LS-US8</t>
+          <t>4MT X 1 1/2" WHITE WASTE PIPE LENGTH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1409,27 +1414,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.6</v>
+        <v>10.79</v>
       </c>
       <c r="H23" s="6" t="n"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SX235981</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>46281.44045966078</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BAUMIT STARTEX MESH ROLL 4MM X 4MM 50M2</t>
+          <t>1 1/4" WHITE WASTE ELBOW 90 DEGREE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1443,35 +1448,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>67.75</v>
-      </c>
-      <c r="F24" t="n">
-        <v>64.72</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.04681705809641533</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="H24" s="6" t="n"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SX235981</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>46281.44045966106</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>89612</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BAUMIT PVC ANGLE (CORNER) BEAD WITH MESH 2.5M</t>
+          <t>1 1/4" WHITE WASTE ELBOW 45 DEGREE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1485,40 +1482,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0.04516129032258065</v>
-      </c>
+        <v>1.68</v>
+      </c>
+      <c r="H25" s="6" t="n"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SX235981</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>46281.44045966119</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>89645</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BAUMIT STAR CONTACT BONDING MORTAR 25KG WHITE</t>
+          <t>1 1/4" MCALPINE P TRAP 76MM SEAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1527,35 +1516,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="F26" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0.04759386567953464</v>
-      </c>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="H26" s="6" t="n"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SX235645</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="n">
-        <v>46281.4404521908</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>89891</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EVODE FIRE RESIST GUN GRADE FOAM 700ML</t>
+          <t>4" 90 DEGREE X 9" BENT PAN CONNECTOR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1569,32 +1550,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11.9</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H27" s="6" t="n"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SX235645</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>46281.44045219098</v>
+          <t>SX235752</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>46281.4404559375</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41318</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BAUMIT N 155 HAMMER IN FIXINGS (BOX OF 100)</t>
+          <t>6MM X 150MM R2 CUTTER YELLOW W/SCREWS 100/BOX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BOX100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1603,35 +1584,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="F28" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0.04706355591311343</v>
-      </c>
+        <v>29.66</v>
+      </c>
+      <c r="H28" s="6" t="n"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SX235645</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="n">
-        <v>46281.44045219109</v>
+          <t>SX235700</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>46281.44045491898</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>93606</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CARRIAGE - DELIVERY CHARGE</t>
+          <t>FLAMCO FLEXVENT 1/2" BOTTLE VENT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1645,32 +1618,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>20.33</v>
+        <v>17.38</v>
       </c>
       <c r="H29" s="6" t="n"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SX235981</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>46281.44045966139</v>
+          <t>SX235682</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>46281.44045400463</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>449890</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAUMIT JOINT SEALING BAND 5.5M (7 ROLLSX5.5M)</t>
+          <t>DEEP HOLE PENCIL SET TAIL SHARPENER DESIGN, 6XREFILLS INCLUDED</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1679,27 +1652,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>59.62</v>
+        <v>7.31</v>
       </c>
       <c r="H30" s="6" t="n"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SX231265</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>46281.44040841375</v>
+          <t>SX235682</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>46281.44045400463</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>572116</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SILIRUB 2 LM SEALANT DARK BROWN</t>
+          <t>EVODE FIRE RESIST GUN GRADE FOAM 700ML</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1713,27 +1686,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9.359999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="H31" s="6" t="n"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SX231265</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>46281.44040841402</v>
+          <t>SX235645</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>46281.4404521875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>83955</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 3/4" X 1/2 348</t>
+          <t>BAUMIT PVC BASE PROFILE THERM 100MM 2M C/W CLIP ON BEAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1747,27 +1720,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="H32" s="6" t="n"/>
+        <v>14.69</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.04853675945753034</v>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SX231346</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>46281.44040930187</v>
+          <t>SX235645</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>46281.4404521875</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>422160</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAUMIT SILIKONTOP K1.5MM COLOUR TINT 25KG 40 NO. TINTED TO 0198</t>
+          <t>TAPING KNIFE 24"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1781,35 +1762,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>88.37</v>
-      </c>
-      <c r="F33" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0.04703791469194313</v>
-      </c>
+        <v>13.37</v>
+      </c>
+      <c r="H33" s="6" t="n"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SX235895</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>46281.44045779933</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>50697</t>
+          <t>50624</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DEWALT DCD796N COMBI DRILL 18V BODY ONLY BRUSHLESS</t>
+          <t>STANLEY AVIATION SNIP ST 214563</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1823,27 +1796,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112.5</v>
+        <v>24.02</v>
       </c>
       <c r="H34" s="6" t="n"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SX231798</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>46281.44041546599</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GLASS / WINDOW PROTECTOR 600 X 25M</t>
+          <t>CORE RECHARGABLE HEADTORCH CLH200</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1857,32 +1830,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25.18</v>
+        <v>13</v>
       </c>
       <c r="H35" s="6" t="n"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="n">
-        <v>46281.44042378209</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>50416</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GYPROC WALLBOARD 1219 X 600 X 12.5MM TE</t>
+          <t>STANLEY CUSHION GRIP WALL BOARD SAW 15556</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SHEET</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1891,35 +1864,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>0.5072727272727273</v>
-      </c>
+        <v>9.710000000000001</v>
+      </c>
+      <c r="H36" s="6" t="n"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>46281.44042378237</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>53878</t>
+          <t>50931</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ADJUSTABLE PRO WORK PLATFORM</t>
+          <t>TALA 150MM-6IN ERGOSOFT S/STEEL JOINTING KNIFE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1933,35 +1898,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>130</v>
-      </c>
-      <c r="F37" t="n">
-        <v>124.41</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>0.04493207941483804</v>
-      </c>
+        <v>12.19</v>
+      </c>
+      <c r="H37" s="6" t="n"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SX232702</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="n">
-        <v>46281.440425774</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>61974</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IRWIN GLASS &amp; TILE DRILLBIT 6MM</t>
+          <t>STANLEY SM18 SNAP OFF BLADES KNIFE 010151</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1975,27 +1932,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5.37</v>
+        <v>3.66</v>
       </c>
       <c r="H38" s="6" t="n"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>46281.44042378295</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>61976</t>
+          <t>51635</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IRWIN GLASS &amp; TILE DRILLBIT 8MM</t>
+          <t>TALA PLASTER TROWEL 11"X4 3/4 SOFT GR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2009,32 +1966,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6.55</v>
+        <v>16.25</v>
       </c>
       <c r="H39" s="6" t="n"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>46281.44042378305</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>73845</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DOSCO 9" PROFESSIONAL CONTRACTOR SET 71084</t>
+          <t>DOSCO COMFORT GRIP DECORATORS SCRAPER 2" 706530</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2043,27 +2000,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>16.15</v>
+        <v>8.66</v>
       </c>
       <c r="H40" s="6" t="n"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>46281.44042378313</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>74100</t>
+          <t>52704</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DOSCO RAD ROLLER 4" ON 17 HANDLE 70011</t>
+          <t>DOSCO COMFORT GRIP DECOR FLEXI FILLING KNIFE 3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2077,27 +2034,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.73</v>
+        <v>11.03</v>
       </c>
       <c r="H41" s="6" t="n"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>46281.44042378321</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>74191</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DOSCO RAD ROLLER SLEEVE SIMULATED WOOL 700262</t>
+          <t>TALA RENDER SCRATCHING FLOAT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2111,27 +2068,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.94</v>
+        <v>9.15</v>
       </c>
       <c r="H42" s="6" t="n"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>46281.44042378329</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>74302</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4" EMULSION SET &amp; GLOSSER SLEEVE</t>
+          <t>TYPHOON MOULDED MASK FFP2 VALVED (3/PK)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2145,27 +2102,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.66</v>
+        <v>11.5</v>
       </c>
       <c r="H43" s="6" t="n"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SX232644</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>46281.44042378337</v>
+          <t>SX235542</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>422160</t>
+          <t>408706</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TAPING KNIFE 24"</t>
+          <t>ABRASIVE DISC 115 X 1.2MM THIN CUT INOX 10 PIECES DT42335TZ-QZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2179,7 +2136,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>13.37</v>
+        <v>14.54</v>
       </c>
       <c r="H44" s="6" t="n"/>
       <c r="I44" t="inlineStr">
@@ -2187,19 +2144,19 @@
           <t>SX235542</t>
         </is>
       </c>
-      <c r="J44" s="7" t="n">
-        <v>46281.44045094141</v>
+      <c r="J44" s="5" t="n">
+        <v>46281.4404509375</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BAUMIT PVC BASE PROFILE THERM 100MM 2M C/W CLIP ON BEAD</t>
+          <t>3/4" IRISH TECTITE STRAIGHT COUPLING</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2213,40 +2170,32 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="F45" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>0.04853675945753034</v>
-      </c>
+        <v>5.97</v>
+      </c>
+      <c r="H45" s="6" t="n"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SX235645</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>46281.44045219089</v>
+          <t>SX235440</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>46281.44044909722</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>52967</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JOINT FILLER PAPER BAG 12.5KG</t>
+          <t>TALA IRISH COPPER PIPE CUTTER 3/4" TA69415</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2255,32 +2204,32 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>32.75</v>
+        <v>24.38</v>
       </c>
       <c r="H46" s="6" t="n"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SX232702</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="n">
-        <v>46281.44042577352</v>
+          <t>SX235440</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>46281.44044909722</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>67462</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GYPROC JOINT FILLER 25KG</t>
+          <t>LUCECO 3W USB HEAD TORCH 150LM W/ MOTION SENSOR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2289,27 +2238,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>40.84</v>
+        <v>13.8</v>
       </c>
       <c r="H47" s="6" t="n"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SX232702</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="n">
-        <v>46281.44042577377</v>
+          <t>SX235440</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>46281.44044909722</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>88970</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.4M MINIMESH ANGLE BEAD</t>
+          <t>5.5M X 3/4" COPPER PIPE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2323,32 +2272,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H48" s="6" t="n"/>
+        <v>60.05</v>
+      </c>
+      <c r="F48" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>-0.0001665001665001665</v>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SX232702</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="n">
-        <v>46281.44042577389</v>
+          <t>SX235440</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>46281.44044909722</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PANEL PINS 25MM X 1.6G 500GM ZINC PLATED</t>
+          <t>NO. 14 X 60 TIMBER TEK 100/BOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2357,27 +2314,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.79</v>
+        <v>23.87</v>
       </c>
       <c r="H49" s="6" t="n"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SX232727</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>46281.44042673074</v>
+          <t>SX235400</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>46281.440448125</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50624</t>
+          <t>442269</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STANLEY AVIATION SNIP ST 214563</t>
+          <t>AC BROOKLYN 3PC STEP DRILL SET LARGE ALUM CASE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2391,32 +2348,32 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>24.02</v>
+        <v>28.98</v>
       </c>
       <c r="H50" s="6" t="n"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="n">
-        <v>46281.44045094048</v>
+          <t>SX235400</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>46281.440448125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>39424</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL COWL 110MM BLACK</t>
+          <t>MDF MOISTURE RESISTANT BOARD 2440 X 1220 X 18MM (2.9768M2 FIBRAPAN HIDROFUGO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SHEET</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2425,32 +2382,32 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3.09</v>
+        <v>46</v>
       </c>
       <c r="H51" s="6" t="n"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SX232992</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>46281.44042764218</v>
+          <t>SX235341</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>46281.44044722222</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>41517</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BLUE DOLPHIN ROUGH SURFACE EXTERIOR TAPE</t>
+          <t>SPAX CHIPBOARD SCREWS YELLOW 3.5X30MM 200/BOX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2459,40 +2416,32 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="F52" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>0.3669902912621359</v>
-      </c>
+        <v>5.81</v>
+      </c>
+      <c r="H52" s="6" t="n"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SX234913</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="n">
-        <v>46281.44044117114</v>
+          <t>SX235341</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>46281.44044722222</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>245909</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BAUMIT N 095 HAMMER IN FIXINGS (BOX OF 100)</t>
+          <t>TUCKS 250S 5X40 WOODSCREW+250S M8 BROWN W/PLUG TUB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2501,32 +2450,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>21.92</v>
+        <v>17.08</v>
       </c>
       <c r="H53" s="6" t="n"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SX235261</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="n">
-        <v>46281.4404462991</v>
+          <t>SX235341</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>46281.44044722222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>41302</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EXT WALL INS ALUMINIUM BASE PROFILE 100MM 2.5M</t>
+          <t>BAUMIT N 095 HAMMER IN FIXINGS (BOX OF 100)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2535,16 +2484,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10.93</v>
+        <v>21.92</v>
       </c>
       <c r="H54" s="6" t="n"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SX234566</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="n">
-        <v>46281.44043687537</v>
+          <t>SX235261</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>46281.4404462963</v>
       </c>
     </row>
     <row r="55">
@@ -2585,19 +2534,19 @@
           <t>SX235261</t>
         </is>
       </c>
-      <c r="J55" s="7" t="n">
-        <v>46281.44044629885</v>
+      <c r="J55" s="5" t="n">
+        <v>46281.4404462963</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>98719</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SOUDAL SILIRUB LM SILICONE 300ML WHITE LM</t>
+          <t>10MM 610 STRAIGHT COUPLER FITTING</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2611,27 +2560,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>9.779999999999999</v>
+        <v>4.77</v>
       </c>
       <c r="H56" s="6" t="n"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SX234566</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>46281.44043687582</v>
+          <t>SX234958</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>46281.44044335649</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>98743</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EVO-SEAL SYSTEM G GUN APPLIED EXPAND FOAM 750ML</t>
+          <t>10MM COMPRESSION 615</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2645,32 +2594,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>8.880000000000001</v>
+        <v>4.16</v>
       </c>
       <c r="H57" s="6" t="n"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SX235981</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="n">
-        <v>46281.44045966129</v>
+          <t>SX234958</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>46281.44044335649</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>51040</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>STANLEY 5 X 18MM SAFETY BLADES 211301</t>
+          <t>SILIRUB 2/S 310ML CARTRIDGE 9.85 PLUS VAT PET TUBE/15 IN CARTON</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2679,27 +2628,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="H58" s="6" t="n"/>
+        <v>15.33</v>
+      </c>
+      <c r="F58" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-149.07</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>-0.9067518248175181</v>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SX235828</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>46281.44045687938</v>
+          <t>SX234913</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>46281.44044116898</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>62830</t>
+          <t>62831</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MAXIFLEX SIZE 8 ULTIMATE ADAPT GLOVE PALM CARDED 42874-08C</t>
+          <t>MAXIFLEX SIZE 9 ULTIMATE ADAPT GLOVE PALM CARDED 42874-09C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2718,22 +2675,22 @@
       <c r="H59" s="6" t="n"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SX234588</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>46281.44043790585</v>
+          <t>SX234755</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MAXIFLEX SIZE 9 ULTIMATE ADAPT GLOVE PALM CARDED 42874-09C</t>
+          <t>100PK ULTRAGRIME ANTIBAC WIPES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2747,7 +2704,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5.43</v>
+        <v>13.68</v>
       </c>
       <c r="H60" s="6" t="n"/>
       <c r="I60" t="inlineStr">
@@ -2755,19 +2712,19 @@
           <t>SX234755</t>
         </is>
       </c>
-      <c r="J60" s="7" t="n">
-        <v>46281.44044000062</v>
+      <c r="J60" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>470555</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SCAN MOULDED VALVED DISP MASK FFP1 (BOX 10)</t>
+          <t>WD40 OIL SMART STRAW CAN 450ML</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2781,32 +2738,32 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>19.92</v>
+        <v>8.84</v>
       </c>
       <c r="H61" s="6" t="n"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SX234588</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="n">
-        <v>46281.44043790615</v>
+          <t>SX234755</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>51987</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>POLYISO THERMAL LINER 92.5MM 2438X1200 (80+12.5)</t>
+          <t>FLEXIBLE DUCTING PVC 127MMX3M WHITE 5" FLEXI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SHEET</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2815,32 +2772,32 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>77.45</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H62" s="6" t="n"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SX234662</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="n">
-        <v>46281.44043892811</v>
+          <t>SX234755</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>100PK ULTRAGRIME ANTIBAC WIPES</t>
+          <t>MEGAMAN NITRILE GLOVE BLACK 50/BOX LGE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2849,7 +2806,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13.68</v>
+        <v>29.53</v>
       </c>
       <c r="H63" s="6" t="n"/>
       <c r="I63" t="inlineStr">
@@ -2857,19 +2814,19 @@
           <t>SX234755</t>
         </is>
       </c>
-      <c r="J63" s="7" t="n">
-        <v>46281.44043999979</v>
+      <c r="J63" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>46192</t>
+          <t>52760</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WD40 OIL SMART STRAW CAN 450ML</t>
+          <t>MAKITA 30-152MM SDS+ CHUCK SHANK ADAPTOR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2883,7 +2840,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>8.84</v>
+        <v>17.34</v>
       </c>
       <c r="H64" s="6" t="n"/>
       <c r="I64" t="inlineStr">
@@ -2891,19 +2848,19 @@
           <t>SX234755</t>
         </is>
       </c>
-      <c r="J64" s="7" t="n">
-        <v>46281.44044000011</v>
+      <c r="J64" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>51987</t>
+          <t>56218</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FLEXIBLE DUCTING PVC 127MMX3M WHITE 5" FLEXI</t>
+          <t>MAKITA BIMETAL HOLE SAW 102MM STANDARD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2917,7 +2874,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>9.699999999999999</v>
+        <v>20.93</v>
       </c>
       <c r="H65" s="6" t="n"/>
       <c r="I65" t="inlineStr">
@@ -2925,24 +2882,24 @@
           <t>SX234755</t>
         </is>
       </c>
-      <c r="J65" s="7" t="n">
-        <v>46281.44044000025</v>
+      <c r="J65" s="5" t="n">
+        <v>46281.44044</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MEGAMAN NITRILE GLOVE BLACK 50/BOX LGE</t>
+          <t>POLYISO THERMAL LINER 92.5MM 2438X1200 (80+12.5)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>SHEET</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2951,27 +2908,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>29.53</v>
+        <v>77.45</v>
       </c>
       <c r="H66" s="6" t="n"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SX234755</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>46281.44044000035</v>
+          <t>SX234662</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>46281.44043892361</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>52760</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MAKITA 30-152MM SDS+ CHUCK SHANK ADAPTOR</t>
+          <t>MAXIFLEX SIZE 8 ULTIMATE ADAPT GLOVE PALM CARDED 42874-08C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2985,27 +2942,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>17.34</v>
+        <v>5.43</v>
       </c>
       <c r="H67" s="6" t="n"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SX234755</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>46281.44044000044</v>
+          <t>SX234588</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>46281.44043790509</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>470555</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MAKITA BIMETAL HOLE SAW 102MM STANDARD</t>
+          <t>SCAN MOULDED VALVED DISP MASK FFP1 (BOX 10)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3019,27 +2976,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20.93</v>
+        <v>19.92</v>
       </c>
       <c r="H68" s="6" t="n"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SX234755</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="n">
-        <v>46281.44044000053</v>
+          <t>SX234588</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>46281.44043790509</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>98719</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10MM 610 STRAIGHT COUPLER FITTING</t>
+          <t>EXT WALL INS ALUMINIUM BASE PROFILE 100MM 2.5M</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3053,27 +3010,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.77</v>
+        <v>10.93</v>
       </c>
       <c r="H69" s="6" t="n"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SX234958</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="n">
-        <v>46281.44044335377</v>
+          <t>SX234566</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>46281.440436875</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>98743</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10MM COMPRESSION 615</t>
+          <t>SOUDAL SILIRUB LM SILICONE 300ML WHITE LM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3087,32 +3044,32 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.16</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H70" s="6" t="n"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SX234958</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="n">
-        <v>46281.44044335408</v>
+          <t>SX234566</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>46281.440436875</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MDF MOISTURE RESISTANT BOARD 2440 X 1220 X 18MM (2.9768M2 FIBRAPAN HIDROFUGO</t>
+          <t>PLUMB CENTRE SOIL COWL 110MM BLACK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SHEET</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3121,32 +3078,32 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>46</v>
+        <v>3.09</v>
       </c>
       <c r="H71" s="6" t="n"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SX235341</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="n">
-        <v>46281.44044722117</v>
+          <t>SX232992</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>46281.44042763889</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPAX CHIPBOARD SCREWS YELLOW 3.5X30MM 200/BOX</t>
+          <t>PANEL PINS 25MM X 1.6G 500GM ZINC PLATED</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3155,27 +3112,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5.81</v>
+        <v>4.79</v>
       </c>
       <c r="H72" s="6" t="n"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SX235341</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="n">
-        <v>46281.44044722156</v>
+          <t>SX232727</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>46281.44042673611</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>245909</t>
+          <t>53878</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TUCKS 250S 5X40 WOODSCREW+250S M8 BROWN W/PLUG TUB</t>
+          <t>ADJUSTABLE PRO WORK PLATFORM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3189,32 +3146,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="H73" s="6" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F73" t="n">
+        <v>124.41</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>0.04493207941483804</v>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SX235341</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>46281.44044722172</v>
+          <t>SX232702</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>46281.44042577546</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NO. 14 X 60 TIMBER TEK 100/BOX</t>
+          <t>JOINT FILLER PAPER BAG 12.5KG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3223,32 +3188,32 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>23.87</v>
+        <v>32.75</v>
       </c>
       <c r="H74" s="6" t="n"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SX235400</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="n">
-        <v>46281.44044812881</v>
+          <t>SX232702</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>46281.44042577546</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>442269</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AC BROOKLYN 3PC STEP DRILL SET LARGE ALUM CASE</t>
+          <t>GYPROC JOINT FILLER 25KG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3257,32 +3222,32 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>28.98</v>
+        <v>40.84</v>
       </c>
       <c r="H75" s="6" t="n"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SX235400</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="n">
-        <v>46281.44044812919</v>
+          <t>SX232702</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>46281.44042577546</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>52967</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TALA IRISH COPPER PIPE CUTTER 3/4" TA69415</t>
+          <t>2.4M MINIMESH ANGLE BEAD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3291,27 +3256,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>24.38</v>
+        <v>1.55</v>
       </c>
       <c r="H76" s="6" t="n"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SX235440</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="n">
-        <v>46281.44044909726</v>
+          <t>SX232702</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>46281.44042577546</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>67462</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LUCECO 3W USB HEAD TORCH 150LM W/ MOTION SENSOR</t>
+          <t>GLASS / WINDOW PROTECTOR 600 X 25M</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3325,32 +3290,32 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>13.8</v>
+        <v>25.18</v>
       </c>
       <c r="H77" s="6" t="n"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SX235440</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="n">
-        <v>46281.44044909752</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CORE RECHARGABLE HEADTORCH CLH200</t>
+          <t>GYPROC WALLBOARD 1219 X 600 X 12.5MM TE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SHEET</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3359,27 +3324,35 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
-      </c>
-      <c r="H78" s="6" t="n"/>
+        <v>8.289999999999999</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>0.5072727272727273</v>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="n">
-        <v>46281.44045094008</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>61974</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STANLEY CUSHION GRIP WALL BOARD SAW 15556</t>
+          <t>IRWIN GLASS &amp; TILE DRILLBIT 6MM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3393,27 +3366,27 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>9.710000000000001</v>
+        <v>5.37</v>
       </c>
       <c r="H79" s="6" t="n"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="n">
-        <v>46281.44045094035</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>61976</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TALA 150MM-6IN ERGOSOFT S/STEEL JOINTING KNIFE</t>
+          <t>IRWIN GLASS &amp; TILE DRILLBIT 8MM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3427,32 +3400,32 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>12.19</v>
+        <v>6.55</v>
       </c>
       <c r="H80" s="6" t="n"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="n">
-        <v>46281.4404509406</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>51085</t>
+          <t>73845</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STANLEY SM18 SNAP OFF BLADES KNIFE 010151</t>
+          <t>DOSCO 9" PROFESSIONAL CONTRACTOR SET 71084</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3461,27 +3434,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3.66</v>
+        <v>16.15</v>
       </c>
       <c r="H81" s="6" t="n"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="n">
-        <v>46281.4404509407</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>51635</t>
+          <t>74100</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TALA PLASTER TROWEL 11"X4 3/4 SOFT GR</t>
+          <t>DOSCO RAD ROLLER 4" ON 17 HANDLE 70011</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3495,27 +3468,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>16.25</v>
+        <v>6.73</v>
       </c>
       <c r="H82" s="6" t="n"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="n">
-        <v>46281.44045094079</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>52700</t>
+          <t>74191</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DOSCO COMFORT GRIP DECORATORS SCRAPER 2" 706530</t>
+          <t>DOSCO RAD ROLLER SLEEVE SIMULATED WOOL 700262</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3529,27 +3502,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>8.66</v>
+        <v>2.94</v>
       </c>
       <c r="H83" s="6" t="n"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="n">
-        <v>46281.44045094087</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>52704</t>
+          <t>74302</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DOSCO COMFORT GRIP DECOR FLEXI FILLING KNIFE 3</t>
+          <t>4" EMULSION SET &amp; GLOSSER SLEEVE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3563,27 +3536,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>11.03</v>
+        <v>8.66</v>
       </c>
       <c r="H84" s="6" t="n"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="n">
-        <v>46281.44045094097</v>
+          <t>SX232644</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>46281.44042378472</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>55364</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TALA RENDER SCRATCHING FLOAT</t>
+          <t>DEWALT DCD996X1 COMBI DRILL 18V BRUSHLESS 1X9AH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3597,27 +3570,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>9.15</v>
+        <v>247.96</v>
       </c>
       <c r="H85" s="6" t="n"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="n">
-        <v>46281.44045094107</v>
+          <t>SX232464</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>46281.44042225694</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>63153</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TYPHOON MOULDED MASK FFP2 VALVED (3/PK)</t>
+          <t>MASKING TAPE BLUE 50MM X 25M</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3631,27 +3604,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>11.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H86" s="6" t="n"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="n">
-        <v>46281.44045094123</v>
+          <t>SX232462</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>46281.44042136574</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>408706</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ABRASIVE DISC 115 X 1.2MM THIN CUT INOX 10 PIECES DT42335TZ-QZ</t>
+          <t>2PT SELF DRILL SCREW WASHER 5.5X60MM HEX 100/PK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3665,27 +3638,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>14.54</v>
+        <v>12</v>
       </c>
       <c r="H87" s="6" t="n"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SX235542</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="n">
-        <v>46281.44045094132</v>
+          <t>SX232356</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>46281.44041952546</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>93606</t>
+          <t>71702</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FLAMCO FLEXVENT 1/2" BOTTLE VENT</t>
+          <t>DULUX TOTAL COVER PURE BRILLIANT WHITE 10L</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3699,32 +3672,32 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>17.38</v>
+        <v>26.82</v>
       </c>
       <c r="H88" s="6" t="n"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SX235682</t>
-        </is>
-      </c>
-      <c r="J88" s="7" t="n">
-        <v>46281.44045400789</v>
+          <t>SX232356</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>46281.44041952546</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>449890</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DEEP HOLE PENCIL SET TAIL SHARPENER DESIGN, 6XREFILLS INCLUDED</t>
+          <t>SELF ADHESIVE DRYWALL SCRIM 75MMX90M GLASS FIBRE BDDJ3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3733,32 +3706,32 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>7.31</v>
+        <v>5.66</v>
       </c>
       <c r="H89" s="6" t="n"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SX235682</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="n">
-        <v>46281.44045400817</v>
+          <t>SX232258</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>46281.44041854166</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>41222</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6MM X 150MM R2 CUTTER YELLOW W/SCREWS 100/BOX</t>
+          <t>DRYWALL SCREWS LOOSE COARSE 125MM X 4.8 200/BOX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BOX100</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3767,32 +3740,32 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29.66</v>
+        <v>19.92</v>
       </c>
       <c r="H90" s="6" t="n"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SX235700</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="n">
-        <v>46281.44045491649</v>
+          <t>SX232258</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>46281.44041854166</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>41426</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL BRANCH 110MM D/S BLACK</t>
+          <t>DRYWALL SCREWS LOOSE COARSE 3.5 X 32 1000/BOX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3801,27 +3774,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>12.13</v>
+        <v>8.52</v>
       </c>
       <c r="H91" s="6" t="n"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="n">
-        <v>46281.44045593853</v>
+          <t>SX232258</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>46281.44041854166</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>82014</t>
+          <t>54120</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1/2" CXC ISOLATING VALVE STRAIGHT</t>
+          <t>DRYWALL SCREWS LOOSE COARSE 4.8 X 150MM 100/BOX</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3835,32 +3808,32 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3.22</v>
+        <v>19.02</v>
       </c>
       <c r="H92" s="6" t="n"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="n">
-        <v>46281.4404559388</v>
+          <t>SX232258</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>46281.44041854166</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>50780</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4MT X 1 1/4" WHITE WASTE PIPE LENGTH</t>
+          <t>KRINO 8X310MM SDS BIT DISPLAY PACK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3869,32 +3842,32 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
       <c r="H93" s="6" t="n"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="n">
-        <v>46281.4404559389</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>89604</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4MT X 1 1/2" WHITE WASTE PIPE LENGTH</t>
+          <t>BLUESPOT MAGNETIC 1/4" NUT DRIVER SET 8 PIECE 6-13MM HEX HEAD B/S14107</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3903,27 +3876,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>10.79</v>
+        <v>11</v>
       </c>
       <c r="H94" s="6" t="n"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="n">
-        <v>46281.440455939</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>51679</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1 1/4" WHITE WASTE ELBOW 90 DEGREE</t>
+          <t>KRINO 6X210MM SDS BIT DISPLAY PACK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3937,27 +3910,27 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.6</v>
+        <v>6.41</v>
       </c>
       <c r="H95" s="6" t="n"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="n">
-        <v>46281.4404559391</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>89612</t>
+          <t>52200</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1 1/4" WHITE WASTE ELBOW 45 DEGREE</t>
+          <t>TALA FLOOR SCRAPER C/W STEEL BLADE TA69237</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3971,27 +3944,27 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.68</v>
+        <v>35.36</v>
       </c>
       <c r="H96" s="6" t="n"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="n">
-        <v>46281.44045593919</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>89645</t>
+          <t>59239</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1 1/4" MCALPINE P TRAP 76MM SEAL</t>
+          <t>COTTON DUST SHEET 12 X 9' LAMINATED</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4005,27 +3978,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>9.970000000000001</v>
+        <v>15.69</v>
       </c>
       <c r="H97" s="6" t="n"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="n">
-        <v>46281.44045593927</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>89891</t>
+          <t>73804</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4" 90 DEGREE X 9" BENT PAN CONNECTOR</t>
+          <t>DOSCO PAINT BRUSH SET 5 PIECE SYNTHETIC 71104</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4039,32 +4012,32 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>8.539999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="H98" s="6" t="n"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SX235752</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="n">
-        <v>46281.44045593937</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>75428</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4.2M 50X22 WHITE DEAL PAO</t>
+          <t>DOSCO PROFESSIONAL MASONRY ROLLER KIT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4073,27 +4046,27 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3.15</v>
+        <v>17.88</v>
       </c>
       <c r="H99" s="6" t="n"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SX235828</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="n">
-        <v>46281.44045687917</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>42566</t>
+          <t>75489</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>REISSER R2 C/W WERA PZ2 BIT 4.5 X 80MM 450/TUB</t>
+          <t>SHED &amp; FENCE BLOCK BRUSH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4107,27 +4080,27 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>23.37</v>
+        <v>6.97</v>
       </c>
       <c r="H100" s="6" t="n"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SX235946</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="n">
-        <v>46281.44045868923</v>
+          <t>SX232062</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>46281.44041755787</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>50697</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RONSEAL BIG HOLE 1.2L FILLER</t>
+          <t>DEWALT DCD796N COMBI DRILL 18V BODY ONLY BRUSHLESS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4141,32 +4114,32 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>13.48</v>
+        <v>112.5</v>
       </c>
       <c r="H101" s="6" t="n"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SX235984</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="n">
-        <v>46281.4404605484</v>
+          <t>SX231798</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>46281.44041546297</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>83924</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 3/4" 315</t>
+          <t>WASHED PLASTERING SAND SMALL BAG (APPROX. 25KG)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4175,27 +4148,27 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4.82</v>
+        <v>3.16</v>
       </c>
       <c r="H102" s="6" t="n"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CA311171</t>
-        </is>
-      </c>
-      <c r="J102" s="7" t="n">
-        <v>46281.44036814972</v>
+          <t>SX231666</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>46281.44041356481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>83974</t>
+          <t>83903</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 3/4" 351</t>
+          <t>PLUMB CENTRE COMPRESSION 1" 310</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4209,27 +4182,27 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4.59</v>
+        <v>6.36</v>
       </c>
       <c r="H103" s="6" t="n"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CA311171</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="n">
-        <v>46281.44036814998</v>
+          <t>SX231666</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>46281.44041356481</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>83925</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TEC7 MS POLYMER ADHESIVE CLEAR</t>
+          <t>PLUMB CENTRE COMPRESSION 1" 315</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4243,32 +4216,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>12.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H104" s="6" t="n"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CA311233</t>
-        </is>
-      </c>
-      <c r="J104" s="7" t="n">
-        <v>46281.44036915404</v>
+          <t>SX231666</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>46281.44041356481</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>96448</t>
+          <t>40761</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TUBOLIT INSULLATION 2MT X 15MM X 9MM WALL (190)</t>
+          <t>HIGH TENSILE HEX BOLT M8 X 25MM ZINC PLATED</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4277,32 +4250,32 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1.86</v>
+        <v>0.24</v>
       </c>
       <c r="H105" s="6" t="n"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>CA311233</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="n">
-        <v>46281.4403691543</v>
+          <t>SX231665</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>46281.44041262731</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>96449</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TUBOLIT INSULATION 2MT X 22MM X 9MM WALL (125)</t>
+          <t>FLAT WASHER ZINC PLATED M6</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4311,32 +4284,32 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2.34</v>
+        <v>0.14</v>
       </c>
       <c r="H106" s="6" t="n"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CA311233</t>
-        </is>
-      </c>
-      <c r="J106" s="7" t="n">
-        <v>46281.44036915442</v>
+          <t>SX231665</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>46281.44041262731</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>96450</t>
+          <t>47126</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TUBOLIT INSULATION 2MT X 28MM X 9MM WALL ( 95)</t>
+          <t>FLAT WASHER ZINC PLATED M8</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4345,27 +4318,27 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2.86</v>
+        <v>0.09</v>
       </c>
       <c r="H107" s="6" t="n"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CA311233</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="n">
-        <v>46281.44036915452</v>
+          <t>SX231665</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>46281.44041262731</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>260704</t>
+          <t>47127</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>THERMOPLUS 500 X 800MM K1 RADIATOR 2274</t>
+          <t>FLAT WASHER ZINC PLATED M10</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4379,32 +4352,32 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>51</v>
+        <v>0.08</v>
       </c>
       <c r="H108" s="6" t="n"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CA311233</t>
-        </is>
-      </c>
-      <c r="J108" s="7" t="n">
-        <v>46281.4403691546</v>
+          <t>SX231665</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>46281.44041262731</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>83955</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IRISH PORTLAND CEMENT 25KG</t>
+          <t>PLUMB CENTRE COMPRESSION 3/4" X 1/2 348</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4413,32 +4386,32 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>7.96</v>
+        <v>3.96</v>
       </c>
       <c r="H109" s="6" t="n"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="n">
-        <v>46281.44037853956</v>
+          <t>SX231346</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>46281.44040930556</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>69649</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RONSEAL MULTI PURPOSE FILLER 3101ML MEDIUM 33367</t>
+          <t>BAUMIT JOINT SEALING BAND 5.5M (7 ROLLSX5.5M)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4447,27 +4420,27 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>9.35</v>
+        <v>59.62</v>
       </c>
       <c r="H110" s="6" t="n"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J110" s="7" t="n">
-        <v>46281.4403785399</v>
+          <t>SX231265</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>46281.44040841435</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>81960</t>
+          <t>572116</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1/2" BSS HP BALLVALVE NYLON PISTON 101A</t>
+          <t>SILIRUB 2 LM SEALANT DARK BROWN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4481,32 +4454,32 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>10.64</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H111" s="6" t="n"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="n">
-        <v>46281.44037854001</v>
+          <t>SX231265</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>46281.44040841435</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4" X 1/2 POLY FLOAT FOR BALLCOCK</t>
+          <t>POLYISO THERMAL LINER MF 38MM 2400X1200 (25+12.5MM)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SHEET</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4515,27 +4488,27 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2.83</v>
+        <v>45.95</v>
       </c>
       <c r="H112" s="6" t="n"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J112" s="7" t="n">
-        <v>46281.4403785401</v>
+          <t>SX230662</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>46281.44040550926</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>83961</t>
+          <t>22615</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 3/4" 350</t>
+          <t>BAUMIT SILIKONTOP K1.5MM WHITE 25KG</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4549,27 +4522,27 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6.65</v>
+        <v>79.37</v>
       </c>
       <c r="H113" s="6" t="n"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J113" s="7" t="n">
-        <v>46281.4403785402</v>
+          <t>SX230661</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>46281.4404045949</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TITAN 45/30 PVC WATER TANK 27GAL AA03</t>
+          <t>PLUMB CENTRE SOIL BEND 110MM X 45DEG D/S BLACK</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4583,27 +4556,35 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>95.91</v>
-      </c>
-      <c r="H114" s="6" t="n"/>
+        <v>7.43</v>
+      </c>
+      <c r="F114" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>0.1040118870728083</v>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J114" s="7" t="n">
-        <v>46281.44037854028</v>
+          <t>SX230630</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>46281.44040258102</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>85045</t>
+          <t>90854</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TITAN PVC LID FOR SLIM 60 TANK AC06</t>
+          <t>GRIFFON HEMP DISPENSER 80G</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4617,27 +4598,27 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>48.65</v>
+        <v>7.71</v>
       </c>
       <c r="H115" s="6" t="n"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J115" s="7" t="n">
-        <v>46281.44037854037</v>
+          <t>SX230630</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>46281.44040258102</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>87501</t>
+          <t>44102</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3/4" POLYWASHER B.M.C. 504</t>
+          <t>HANGER 2-HOLE HORIZ. BOTTOM 155 X50X8MM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4651,27 +4632,27 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.35</v>
+        <v>5.4</v>
       </c>
       <c r="H116" s="6" t="n"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J116" s="7" t="n">
-        <v>46281.44037854045</v>
+          <t>SX230388</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>46281.44040079861</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>260759</t>
+          <t>71477</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>THERMOPLUS 600 X 1100MM K2 RADIATOR 6501</t>
+          <t>DULUX WEATHERSHIELD PURE BRILLIANT WHITE 11L</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4685,27 +4666,27 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>142</v>
+        <v>55.1</v>
       </c>
       <c r="H117" s="6" t="n"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J117" s="7" t="n">
-        <v>46281.44037854054</v>
+          <t>SX230388</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>46281.44040079861</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>461713</t>
+          <t>461686</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TUCKS METAL SPEED PLUG 300S 4.5X35MM ZP TUB</t>
+          <t>FATMAX 120.60CM TORPEDO 3PK SUMMER PROMO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4719,27 +4700,27 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>30.85</v>
+        <v>89.42</v>
       </c>
       <c r="H118" s="6" t="n"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>RH593039</t>
-        </is>
-      </c>
-      <c r="J118" s="7" t="n">
-        <v>46281.44037854065</v>
+          <t>SX230388</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>46281.44040079861</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.0M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
+          <t>2.4M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4753,27 +4734,27 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5.37</v>
+        <v>4.3</v>
       </c>
       <c r="H119" s="6" t="n"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>RH593157</t>
-        </is>
-      </c>
-      <c r="J119" s="7" t="n">
-        <v>46281.44038052983</v>
+          <t>SX230354</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>46281.44039837963</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MCALPINE WASHING MACHINE TRAP SINGLE SPIGOT WM2</t>
+          <t>PLUMB CENTRE SOIL BEND 110MM X 90DEG S/S BLACK</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4787,27 +4768,27 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9.470000000000001</v>
+        <v>6.43</v>
       </c>
       <c r="H120" s="6" t="n"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SX12284_168143390</t>
-        </is>
-      </c>
-      <c r="J120" s="7" t="n">
-        <v>46281.44038706453</v>
+          <t>SX230310</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>89647</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1 1/2" MCALPINE P TRAP 76MM SEAL -13.48</t>
+          <t>PLUMB CENTRE SOIL BEND 110MM X 45DEG S/S BLACK</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4821,27 +4802,27 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4.01</v>
+        <v>5.88</v>
       </c>
       <c r="H121" s="6" t="n"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SX12284_168143390</t>
-        </is>
-      </c>
-      <c r="J121" s="7" t="n">
-        <v>46281.44038706479</v>
+          <t>SX230310</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>31957</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL BEND 110MM X 90DEG S/S BLACK</t>
+          <t>PLUMB CENTRE SOIL COUPLER 110MM D/S BLACK</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4855,7 +4836,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6.43</v>
+        <v>4.84</v>
       </c>
       <c r="H122" s="6" t="n"/>
       <c r="I122" t="inlineStr">
@@ -4863,19 +4844,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J122" s="7" t="n">
-        <v>46281.4403963969</v>
+      <c r="J122" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>31955</t>
+          <t>31959</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL BEND 110MM X 45DEG D/S BLACK</t>
+          <t>PLUMB CENTRE SOIL BRANCH 110MM T/S BLACK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4889,35 +4870,27 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="F123" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H123" s="6" t="n">
-        <v>0.1040118870728083</v>
-      </c>
+        <v>9.83</v>
+      </c>
+      <c r="H123" s="6" t="n"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SX230630</t>
-        </is>
-      </c>
-      <c r="J123" s="7" t="n">
-        <v>46281.44040258385</v>
+          <t>SX230310</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL BEND 110MM X 45DEG S/S BLACK</t>
+          <t>PLUMB CENTRE STRAP ON BOSS 110MM BLACK</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4931,7 +4904,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5.88</v>
+        <v>6.2</v>
       </c>
       <c r="H124" s="6" t="n"/>
       <c r="I124" t="inlineStr">
@@ -4939,19 +4912,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J124" s="7" t="n">
-        <v>46281.44039639729</v>
+      <c r="J124" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL COUPLER 110MM D/S BLACK</t>
+          <t>PLUMB CENTRE BOSS ADAPTOR 32MM BLACK</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4965,7 +4938,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4.84</v>
+        <v>2.77</v>
       </c>
       <c r="H125" s="6" t="n"/>
       <c r="I125" t="inlineStr">
@@ -4973,19 +4946,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J125" s="7" t="n">
-        <v>46281.44039639738</v>
+      <c r="J125" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>31959</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE SOIL BRANCH 110MM T/S BLACK</t>
+          <t>PLUMB CENTRE BOSS ADAPTOR 40MM BLACK</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4999,7 +4972,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>9.83</v>
+        <v>2.77</v>
       </c>
       <c r="H126" s="6" t="n"/>
       <c r="I126" t="inlineStr">
@@ -5007,19 +4980,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J126" s="7" t="n">
-        <v>46281.44039639748</v>
+      <c r="J126" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>31968</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE STRAP ON BOSS 110MM BLACK</t>
+          <t>1 1/2" WHITE WASTE STRAIGHT CONNECTOR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5033,7 +5006,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6.2</v>
+        <v>1.81</v>
       </c>
       <c r="H127" s="6" t="n"/>
       <c r="I127" t="inlineStr">
@@ -5041,19 +5014,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J127" s="7" t="n">
-        <v>46281.44039639757</v>
+      <c r="J127" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>89637</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE BOSS ADAPTOR 32MM BLACK</t>
+          <t>1 1/4" WHITE WASTE TEE 91.5 DEGREE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5067,7 +5040,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="H128" s="6" t="n"/>
       <c r="I128" t="inlineStr">
@@ -5075,19 +5048,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J128" s="7" t="n">
-        <v>46281.44039639765</v>
+      <c r="J128" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>31970</t>
+          <t>89639</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE BOSS ADAPTOR 40MM BLACK</t>
+          <t>1 1/2" WHITE WASTE TEE 91.5 DEGREE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5101,7 +5074,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="H129" s="6" t="n"/>
       <c r="I129" t="inlineStr">
@@ -5109,19 +5082,19 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J129" s="7" t="n">
-        <v>46281.44039639775</v>
+      <c r="J129" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1 1/2" WHITE WASTE STRAIGHT CONNECTOR</t>
+          <t>MFP BLACK 110MM SOIL PIPE CLIP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5135,7 +5108,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="H130" s="6" t="n"/>
       <c r="I130" t="inlineStr">
@@ -5143,24 +5116,24 @@
           <t>SX230310</t>
         </is>
       </c>
-      <c r="J130" s="7" t="n">
-        <v>46281.44039639801</v>
+      <c r="J130" s="5" t="n">
+        <v>46281.44039640046</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1 1/4" WHITE WASTE TEE 91.5 DEGREE</t>
+          <t>4.8M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5169,32 +5142,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H131" s="6" t="n"/>
+        <v>8.59</v>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SX230310</t>
-        </is>
-      </c>
-      <c r="J131" s="7" t="n">
-        <v>46281.44039639809</v>
+          <t>SX230225</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>46281.44039412037</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>89639</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1 1/2" WHITE WASTE TEE 91.5 DEGREE</t>
+          <t>KORE EXTERNAL PLINTH 1200X600X20MM EPS200 WHITE 21.6M2/BALE Supplier : AIRPACKS LTD(KORE INSULATION) Delivery Dkt. Num : 042299 Delivery Dkt. Date : 8/6/26</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BALE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5203,27 +5175,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H132" s="6" t="n"/>
+        <v>71.90000000000001</v>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SX230310</t>
-        </is>
-      </c>
-      <c r="J132" s="7" t="n">
-        <v>46281.44039639817</v>
+          <t>SX230140</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>46281.44039113426</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>89685</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MFP BLACK 110MM SOIL PIPE CLIP</t>
+          <t>MCALPINE WASHING MACHINE TRAP SINGLE SPIGOT WM2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5237,32 +5208,32 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2.28</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H133" s="6" t="n"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SX230310</t>
-        </is>
-      </c>
-      <c r="J133" s="7" t="n">
-        <v>46281.44039639826</v>
+          <t>SX12284_168143390</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>46281.44038706018</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>89647</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2.4M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
+          <t>1 1/2" MCALPINE P TRAP 76MM SEAL -13.48</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5271,27 +5242,27 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4.3</v>
+        <v>4.01</v>
       </c>
       <c r="H134" s="6" t="n"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SX230354</t>
-        </is>
-      </c>
-      <c r="J134" s="7" t="n">
-        <v>46281.44039837753</v>
+          <t>SX12284_168143390</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>46281.44038706018</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>D029/111</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HANGER 2-HOLE HORIZ. BOTTOM 155 X50X8MM</t>
+          <t>SMALL DEHUMIDIFIER On Hire From 8/9/26 To 10/9/26 @ 27.54 Per Day For 2 Days</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5305,27 +5276,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H135" s="6" t="n"/>
+        <v>55.08</v>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SX230388</t>
-        </is>
-      </c>
-      <c r="J135" s="7" t="n">
-        <v>46281.44040079451</v>
+          <t>SN81079</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>46281.44038465278</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>50780</t>
+          <t>D029/83</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>KRINO 8X310MM SDS BIT DISPLAY PACK</t>
+          <t>SMALL DEHUMIDIFIER On Hire From 8/9/26 To 10/9/26 @ 27.54 Per Day For 2 Days</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5339,27 +5309,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="H136" s="6" t="n"/>
+        <v>55.08</v>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J136" s="7" t="n">
-        <v>46281.44041755493</v>
+          <t>SN81079</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>46281.44038465278</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>71477</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DULUX WEATHERSHIELD PURE BRILLIANT WHITE 11L</t>
+          <t>80PK ULTRAGRIME POWER SCRUB WIPES</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5373,27 +5342,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="H137" s="6" t="n"/>
+        <v>15.08</v>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>SX230388</t>
-        </is>
-      </c>
-      <c r="J137" s="7" t="n">
-        <v>46281.44040079492</v>
+          <t>SN342622</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>46281.44038366898</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>461686</t>
+          <t>260737</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FATMAX 120.60CM TORPEDO 3PK SUMMER PROMO</t>
+          <t>THERMOPLUS 500 X 400MM K2 RADIATOR 2039</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5407,27 +5375,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>89.42</v>
-      </c>
-      <c r="H138" s="6" t="n"/>
+        <v>48</v>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SX230388</t>
-        </is>
-      </c>
-      <c r="J138" s="7" t="n">
-        <v>46281.44040079501</v>
+          <t>SN342622</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>46281.44038366898</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>90854</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GRIFFON HEMP DISPENSER 80G</t>
+          <t>PLUMB CENTRE COMPRESSION 1" 318</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5441,27 +5408,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="H139" s="6" t="n"/>
+        <v>11.08</v>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SX230630</t>
-        </is>
-      </c>
-      <c r="J139" s="7" t="n">
-        <v>46281.44040258413</v>
+          <t>SN341439</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>46281.44038268518</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>260739</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BAUMIT SILIKONTOP K1.5MM WHITE 25KG</t>
+          <t>THERMOPLUS 500 X 600MM K2 RADIATOR 3059</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5475,32 +5441,32 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>79.37</v>
+        <v>69</v>
       </c>
       <c r="H140" s="6" t="n"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SX230661</t>
-        </is>
-      </c>
-      <c r="J140" s="7" t="n">
-        <v>46281.44040459942</v>
+          <t>SN341278</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>46281.44038170139</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>455158</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>POLYISO THERMAL LINER MF 38MM 2400X1200 (25+12.5MM)</t>
+          <t>MASONMATE M10 X 100 HEX SCREWBOLT OPT1 ZP 25S</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SHEET</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5509,27 +5475,27 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>45.95</v>
+        <v>1.35</v>
       </c>
       <c r="H141" s="6" t="n"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>SX230662</t>
-        </is>
-      </c>
-      <c r="J141" s="7" t="n">
-        <v>46281.44040551349</v>
+          <t>SN341278</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>46281.44038170139</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>83985</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HIGH TENSILE HEX BOLT M8 X 25MM ZINC PLATED</t>
+          <t>PLUMB CENTRE COMPRESSION 1" 351</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5543,32 +5509,32 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.24</v>
+        <v>11.18</v>
       </c>
       <c r="H142" s="6" t="n"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SX231665</t>
-        </is>
-      </c>
-      <c r="J142" s="7" t="n">
-        <v>46281.44041263111</v>
+          <t>SN341278</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>46281.44038170139</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FLAT WASHER ZINC PLATED M6</t>
+          <t>3.0M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5577,32 +5543,32 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.14</v>
+        <v>5.37</v>
       </c>
       <c r="H143" s="6" t="n"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SX231665</t>
-        </is>
-      </c>
-      <c r="J143" s="7" t="n">
-        <v>46281.44041263137</v>
+          <t>RH593157</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>46281.44038053241</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FLAT WASHER ZINC PLATED M8</t>
+          <t>IRISH PORTLAND CEMENT 25KG</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5611,27 +5577,27 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.09</v>
+        <v>7.96</v>
       </c>
       <c r="H144" s="6" t="n"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SX231665</t>
-        </is>
-      </c>
-      <c r="J144" s="7" t="n">
-        <v>46281.44041263148</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>47127</t>
+          <t>69649</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FLAT WASHER ZINC PLATED M10</t>
+          <t>RONSEAL MULTI PURPOSE FILLER 3101ML MEDIUM 33367</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5645,32 +5611,32 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.08</v>
+        <v>9.35</v>
       </c>
       <c r="H145" s="6" t="n"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SX231665</t>
-        </is>
-      </c>
-      <c r="J145" s="7" t="n">
-        <v>46281.44041263157</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>81960</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>WASHED PLASTERING SAND SMALL BAG (APPROX. 25KG)</t>
+          <t>1/2" BSS HP BALLVALVE NYLON PISTON 101A</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5679,27 +5645,27 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3.16</v>
+        <v>10.64</v>
       </c>
       <c r="H146" s="6" t="n"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SX231666</t>
-        </is>
-      </c>
-      <c r="J146" s="7" t="n">
-        <v>46281.44041356531</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>83903</t>
+          <t>82052</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 1" 310</t>
+          <t>4" X 1/2 POLY FLOAT FOR BALLCOCK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5713,27 +5679,27 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6.36</v>
+        <v>2.83</v>
       </c>
       <c r="H147" s="6" t="n"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SX231666</t>
-        </is>
-      </c>
-      <c r="J147" s="7" t="n">
-        <v>46281.44041356556</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>83925</t>
+          <t>83961</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 1" 315</t>
+          <t>PLUMB CENTRE COMPRESSION 3/4" 350</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5747,27 +5713,27 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>8.390000000000001</v>
+        <v>6.65</v>
       </c>
       <c r="H148" s="6" t="n"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SX231666</t>
-        </is>
-      </c>
-      <c r="J148" s="7" t="n">
-        <v>46281.44041356567</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BLUESPOT MAGNETIC 1/4" NUT DRIVER SET 8 PIECE 6-13MM HEX HEAD B/S14107</t>
+          <t>TITAN 45/30 PVC WATER TANK 27GAL AA03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5781,27 +5747,27 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>11</v>
+        <v>95.91</v>
       </c>
       <c r="H149" s="6" t="n"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J149" s="7" t="n">
-        <v>46281.44041755464</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>51679</t>
+          <t>85045</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>KRINO 6X210MM SDS BIT DISPLAY PACK</t>
+          <t>TITAN PVC LID FOR SLIM 60 TANK AC06</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5815,27 +5781,27 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6.41</v>
+        <v>48.65</v>
       </c>
       <c r="H150" s="6" t="n"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J150" s="7" t="n">
-        <v>46281.44041755512</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>52200</t>
+          <t>87501</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TALA FLOOR SCRAPER C/W STEEL BLADE TA69237</t>
+          <t>3/4" POLYWASHER B.M.C. 504</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5849,27 +5815,27 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>35.36</v>
+        <v>0.35</v>
       </c>
       <c r="H151" s="6" t="n"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J151" s="7" t="n">
-        <v>46281.44041755523</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>59239</t>
+          <t>260759</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>COTTON DUST SHEET 12 X 9' LAMINATED</t>
+          <t>THERMOPLUS 600 X 1100MM K2 RADIATOR 6501</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5883,27 +5849,27 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15.69</v>
+        <v>142</v>
       </c>
       <c r="H152" s="6" t="n"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J152" s="7" t="n">
-        <v>46281.44041755541</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>461713</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DOSCO PAINT BRUSH SET 5 PIECE SYNTHETIC 71104</t>
+          <t>TUCKS METAL SPEED PLUG 300S 4.5X35MM ZP TUB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5917,27 +5883,27 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6.47</v>
+        <v>30.85</v>
       </c>
       <c r="H153" s="6" t="n"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J153" s="7" t="n">
-        <v>46281.44041755549</v>
+          <t>RH593039</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>46281.44037854167</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>52238</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DOSCO PROFESSIONAL MASONRY ROLLER KIT</t>
+          <t>KRINO 10X210MM SDS BIT DISPLAY PACK</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5951,27 +5917,27 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>17.88</v>
+        <v>7.8</v>
       </c>
       <c r="H154" s="6" t="n"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J154" s="7" t="n">
-        <v>46281.44041755566</v>
+          <t>N751006</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="n">
+        <v>46281.44037641204</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>75489</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SHED &amp; FENCE BLOCK BRUSH</t>
+          <t>DEWALT SDS HAMMER BODY ONLY 18V DWDCH273N-XJ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5985,32 +5951,32 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6.97</v>
+        <v>227.62</v>
       </c>
       <c r="H155" s="6" t="n"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SX232062</t>
-        </is>
-      </c>
-      <c r="J155" s="7" t="n">
-        <v>46281.44041755573</v>
+          <t>N751006</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>46281.44037641204</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>52239</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SELF ADHESIVE DRYWALL SCRIM 75MMX90M GLASS FIBRE BDDJ3</t>
+          <t>KRINO 12X210MM SDS BIT DISPLAY PACK</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ROLL</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6019,32 +5985,32 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5.66</v>
+        <v>7.8</v>
       </c>
       <c r="H156" s="6" t="n"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SX232258</t>
-        </is>
-      </c>
-      <c r="J156" s="7" t="n">
-        <v>46281.44041854121</v>
+          <t>N751006</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>46281.44037641204</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>41222</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DRYWALL SCREWS LOOSE COARSE 125MM X 4.8 200/BOX</t>
+          <t>TRACER LASER MEASURE ALM100 ALM100 TRACER</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6053,32 +6019,40 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="H157" s="6" t="n"/>
+        <v>88.62</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="H157" s="6" t="n">
+        <v>87.62</v>
+      </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SX232258</t>
-        </is>
-      </c>
-      <c r="J157" s="7" t="n">
-        <v>46281.44041854141</v>
+          <t>LY203947</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>46281.44037534722</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>41426</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DRYWALL SCREWS LOOSE COARSE 3.5 X 32 1000/BOX</t>
+          <t>SEWER GULLY GRID 160 X 160MM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6087,27 +6061,35 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="H158" s="6" t="n"/>
+        <v>5.51</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H158" s="6" t="n">
+        <v>4.51</v>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>SX232258</t>
-        </is>
-      </c>
-      <c r="J158" s="7" t="n">
-        <v>46281.44041854149</v>
+          <t>LY203947</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>46281.44037534722</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>54120</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DRYWALL SCREWS LOOSE COARSE 4.8 X 150MM 100/BOX</t>
+          <t>ADJUSTABLE &amp; LINKING PRO WORK PLATFORM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6121,27 +6103,35 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="H159" s="6" t="n"/>
+        <v>142.27</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>141.27</v>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>141.27</v>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>SX232258</t>
-        </is>
-      </c>
-      <c r="J159" s="7" t="n">
-        <v>46281.44041854158</v>
+          <t>CA313706</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>46281.44037319445</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>50069</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2PT SELF DRILL SCREW WASHER 5.5X60MM HEX 100/PK</t>
+          <t>ARC FOAM GUN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6155,32 +6145,32 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>12</v>
+        <v>33.46</v>
       </c>
       <c r="H160" s="6" t="n"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SX232356</t>
-        </is>
-      </c>
-      <c r="J160" s="7" t="n">
-        <v>46281.44041952205</v>
+          <t>CA313706</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="n">
+        <v>46281.44037319445</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>71702</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DULUX TOTAL COVER PURE BRILLIANT WHITE 10L</t>
+          <t>POLYISO UNDERFLOOR INSULAT 1200X2400X100MM</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>SHEET</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6189,27 +6179,35 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>26.82</v>
-      </c>
-      <c r="H161" s="6" t="n"/>
+        <v>56.48</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>55.48</v>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SX232356</t>
-        </is>
-      </c>
-      <c r="J161" s="7" t="n">
-        <v>46281.44041952214</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MASKING TAPE BLUE 50MM X 25M</t>
+          <t>CONCRETE SCREW TORX 30 7.5X62 100/BOX</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6223,27 +6221,27 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>8.119999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H162" s="6" t="n"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>SX232462</t>
-        </is>
-      </c>
-      <c r="J162" s="7" t="n">
-        <v>46281.44042136033</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>55364</t>
+          <t>46923</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DEWALT DCD996X1 COMBI DRILL 18V BRUSHLESS 1X9AH</t>
+          <t>CUP SQUARE BOLT &amp; NUT 10X130</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6257,32 +6255,32 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>247.96</v>
+        <v>0.96</v>
       </c>
       <c r="H163" s="6" t="n"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SX232464</t>
-        </is>
-      </c>
-      <c r="J163" s="7" t="n">
-        <v>46281.4404222552</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>47227</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>4.8M 50X22 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
+          <t>MUDGUARD WASHER M6 X 30MM</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -6291,32 +6289,32 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2.11</v>
+        <v>0.09</v>
       </c>
       <c r="H164" s="6" t="n"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J164" s="7" t="n">
-        <v>46281.44036722396</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>414122</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FISCHER 79553 PVC COATED GALV BAND 10MT X 14MM</t>
+          <t>SDS+ MASONRY DRILL BIT 5.0 X 160MM 4 CUTTER</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ROLL</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -6325,32 +6323,40 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>16</v>
-      </c>
-      <c r="H165" s="6" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>2.09</v>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J165" s="7" t="n">
-        <v>46281.44036722426</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>414138</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BLACK L 450MM W 8MM CABLE TIE PACK OF 100</t>
+          <t>SDS+ MASONRY DRILL BIT 12.0 X 450MM 4 CUTTER</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PACK</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -6359,27 +6365,35 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="H166" s="6" t="n"/>
+        <v>15.21</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="H166" s="6" t="n">
+        <v>14.21</v>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J166" s="7" t="n">
-        <v>46281.44036722437</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>46004</t>
+          <t>442612</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ZP COACH SCREW HWX HEAD 8X80MM</t>
+          <t>MASONMATE THROUGHBOLT M10 X 65MM OPT7 100S</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6393,27 +6407,27 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H167" s="6" t="n"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J167" s="7" t="n">
-        <v>46281.44036722447</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>47068</t>
+          <t>442616</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HEX COACH SCREWS 10X100MM ZINC PLATED</t>
+          <t>MASONMATE THROUGHBOLT M10 X 120MM OPT7 50S</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6427,27 +6441,27 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H168" s="6" t="n"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J168" s="7" t="n">
-        <v>46281.44036722456</v>
+          <t>CA313212</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>46281.44037021991</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MUDGUARD WASHER M8 X 30MM</t>
+          <t>TEC7 MS POLYMER ADHESIVE CLEAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6461,32 +6475,32 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.21</v>
+        <v>12.35</v>
       </c>
       <c r="H169" s="6" t="n"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J169" s="7" t="n">
-        <v>46281.44036722464</v>
+          <t>CA311233</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>46281.44036915509</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>67103</t>
+          <t>96448</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BLUE PROTECTIVE FOIL 500X100M</t>
+          <t>TUBOLIT INSULLATION 2MT X 15MM X 9MM WALL (190)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6495,32 +6509,32 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>42.82</v>
+        <v>1.86</v>
       </c>
       <c r="H170" s="6" t="n"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J170" s="7" t="n">
-        <v>46281.44036722472</v>
+          <t>CA311233</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="n">
+        <v>46281.44036915509</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>449505</t>
+          <t>96449</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SPADER HOLDFAST POZI 3,5X50 WOOD SCREW CSK 950 / TUB</t>
+          <t>TUBOLIT INSULATION 2MT X 22MM X 9MM WALL (125)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6529,27 +6543,27 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>25</v>
+        <v>2.34</v>
       </c>
       <c r="H171" s="6" t="n"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>CA308662</t>
-        </is>
-      </c>
-      <c r="J171" s="7" t="n">
-        <v>46281.4403672248</v>
+          <t>CA311233</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>46281.44036915509</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>88970</t>
+          <t>96450</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5.5M X 3/4" COPPER PIPE</t>
+          <t>TUBOLIT INSULATION 2MT X 28MM X 9MM WALL ( 95)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6563,35 +6577,27 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>60.05</v>
-      </c>
-      <c r="F172" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="G172" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H172" s="6" t="n">
-        <v>-0.0001665001665001665</v>
-      </c>
+        <v>2.86</v>
+      </c>
+      <c r="H172" s="6" t="n"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SX235440</t>
-        </is>
-      </c>
-      <c r="J172" s="7" t="n">
-        <v>46281.44044909777</v>
+          <t>CA311233</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>46281.44036915509</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>260704</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PLUMB CENTRE COMPRESSION 1" 318</t>
+          <t>THERMOPLUS 500 X 800MM K1 RADIATOR 2274</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6605,26 +6611,27 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>11.08</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="H173" s="6" t="n"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SN341439</t>
-        </is>
-      </c>
-      <c r="J173" s="7" t="n">
-        <v>46281.44038268182</v>
+          <t>CA311233</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="n">
+        <v>46281.44036915509</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>83924</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>80PK ULTRAGRIME POWER SCRUB WIPES</t>
+          <t>PLUMB CENTRE COMPRESSION 3/4" 315</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6638,26 +6645,27 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>15.08</v>
-      </c>
+        <v>4.82</v>
+      </c>
+      <c r="H174" s="6" t="n"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SN342622</t>
-        </is>
-      </c>
-      <c r="J174" s="7" t="n">
-        <v>46281.44038366416</v>
+          <t>CA311171</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>46281.44036814815</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>260737</t>
+          <t>83974</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>THERMOPLUS 500 X 400MM K2 RADIATOR 2039</t>
+          <t>PLUMB CENTRE COMPRESSION 3/4" 351</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6671,31 +6679,32 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>48</v>
-      </c>
+        <v>4.59</v>
+      </c>
+      <c r="H175" s="6" t="n"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SN342622</t>
-        </is>
-      </c>
-      <c r="J175" s="7" t="n">
-        <v>46281.44038366443</v>
+          <t>CA311171</t>
+        </is>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>46281.44036814815</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>4.8M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
+          <t>FISCHER 79553 PVC COATED GALV BAND 10MT X 14MM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6704,31 +6713,32 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>8.59</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H176" s="6" t="n"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>SX230225</t>
-        </is>
-      </c>
-      <c r="J176" s="7" t="n">
-        <v>46281.44039411465</v>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>46281.44036722223</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>D029/111</t>
+          <t>34961</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SMALL DEHUMIDIFIER On Hire From 8/9/26 To 10/9/26 @ 27.54 Per Day For 2 Days</t>
+          <t>BLACK L 450MM W 8MM CABLE TIE PACK OF 100</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>EACH</t>
+          <t>PACK</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6737,26 +6747,27 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>55.08</v>
-      </c>
+        <v>11.37</v>
+      </c>
+      <c r="H177" s="6" t="n"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SN81079</t>
-        </is>
-      </c>
-      <c r="J177" s="7" t="n">
-        <v>46281.44038465163</v>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>46281.44036722223</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>D029/83</t>
+          <t>46004</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SMALL DEHUMIDIFIER On Hire From 8/9/26 To 10/9/26 @ 27.54 Per Day For 2 Days</t>
+          <t>ZP COACH SCREW HWX HEAD 8X80MM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6770,26 +6781,27 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>55.08</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="H178" s="6" t="n"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SN81079</t>
-        </is>
-      </c>
-      <c r="J178" s="7" t="n">
-        <v>46281.44038465223</v>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>46281.44036722223</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SILIRUB 2/S 310ML CARTRIDGE 9.85 PLUS VAT PET TUBE/15 IN CARTON</t>
+          <t>HEX COACH SCREWS 10X100MM ZINC PLATED</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6803,40 +6815,32 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="F179" t="n">
-        <v>164.4</v>
-      </c>
-      <c r="G179" t="n">
-        <v>-149.07</v>
-      </c>
-      <c r="H179" s="6" t="n">
-        <v>-0.9067518248175181</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H179" s="6" t="n"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SX234913</t>
-        </is>
-      </c>
-      <c r="J179" s="7" t="n">
-        <v>46281.44044117146</v>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>46281.44036722223</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KORE EXTERNAL PLINTH 1200X600X20MM EPS200 WHITE 21.6M2/BALE Supplier : AIRPACKS LTD(KORE INSULATION) Delivery Dkt. Num : 042299 Delivery Dkt. Date : 8/6/26</t>
+          <t>MUDGUARD WASHER M8 X 30MM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BALE</t>
+          <t>EACH</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -6845,19 +6849,92 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>71.90000000000001</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="H180" s="6" t="n"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SX230140</t>
-        </is>
-      </c>
-      <c r="J180" s="7" t="n">
-        <v>46281.44039113048</v>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>46281.44036722223</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>67103</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>BLUE PROTECTIVE FOIL 500X100M</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>EACH</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="H181" s="6" t="n"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>46281.44036722223</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>449505</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SPADER HOLDFAST POZI 3,5X50 WOOD SCREW CSK 950 / TUB</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>25</v>
+      </c>
+      <c r="H182" s="6" t="n"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>CA308662</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>46281.44036722223</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J1">
+    <sortState ref="A2:J182">
+      <sortCondition descending="1" ref="J1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967293" verticalDpi="4294967293"/>
 </worksheet>
@@ -7065,7 +7142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1949"/>
+  <dimension ref="A1:H1953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -70153,6 +70230,132 @@
       <c r="G1949" t="inlineStr">
         <is>
           <t>SX235440</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>14/9/26</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>449886</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>NITRILE DIPPED GLOVES XL</t>
+        </is>
+      </c>
+      <c r="F1950" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="G1950" t="inlineStr">
+        <is>
+          <t>CA316114</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>15/9/26</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>96335</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>CARBERY ATTIC TANK JACKET (PACK 10) AT44. AT58. AT45R, AT60R, AT80R</t>
+        </is>
+      </c>
+      <c r="F1951" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="G1951" t="inlineStr">
+        <is>
+          <t>SX236186</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>11/9/26</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>CARRIAGE - DELIVERY CHARGE</t>
+        </is>
+      </c>
+      <c r="E1952" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="G1952" t="inlineStr">
+        <is>
+          <t>SX235981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>11/9/26</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>CARRIAGE - DELIVERY CHARGE</t>
+        </is>
+      </c>
+      <c r="E1953" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1953" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="G1953" t="inlineStr">
+        <is>
+          <t>SX235981</t>
         </is>
       </c>
     </row>

--- a/Chadwicks_FULL_INVOICES_TEST_NO_MATERIAL_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
+++ b/Chadwicks_FULL_INVOICES_TEST_NO_MATERIAL_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>46281.54438446146</v>
+        <v>46282.69722786799</v>
       </c>
     </row>
     <row r="3">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>46281.54438446133</v>
+        <v>46282.69722786789</v>
       </c>
     </row>
     <row r="4">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>46281.54438446119</v>
+        <v>46282.6972278678</v>
       </c>
     </row>
     <row r="5">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>46281.54438446102</v>
+        <v>46282.69722786768</v>
       </c>
     </row>
     <row r="6">
@@ -809,13 +809,13 @@
         <v>3.24</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>1.24</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.04516129032258065</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46281.54438446047</v>
+        <v>46282.69722786742</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46281.54438325853</v>
+        <v>46282.69722696375</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>46281.54438180056</v>
+        <v>46282.69722614333</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>46281.54438085141</v>
+        <v>46282.69722530319</v>
       </c>
     </row>
     <row r="10">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>46281.54438085121</v>
+        <v>46282.69722530272</v>
       </c>
     </row>
     <row r="11">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>46281.54438085092</v>
+        <v>46282.69722530244</v>
       </c>
     </row>
     <row r="12">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>46281.54437980019</v>
+        <v>46282.69722440109</v>
       </c>
     </row>
     <row r="13">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>46281.54437880626</v>
+        <v>46282.69722352853</v>
       </c>
     </row>
     <row r="14">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>46281.54437780003</v>
+        <v>46282.69722270758</v>
       </c>
     </row>
     <row r="15">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>46281.54437779972</v>
+        <v>46282.69722270725</v>
       </c>
     </row>
     <row r="16">
@@ -7142,7 +7142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1953"/>
+  <dimension ref="A1:H1955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -70354,6 +70354,72 @@
         <v>20.33</v>
       </c>
       <c r="G1953" t="inlineStr">
+        <is>
+          <t>SX235981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>11/9/26</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>22502</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>BAUMIT PVC ANGLE (CORNER) BEAD WITH MESH 2.5M</t>
+        </is>
+      </c>
+      <c r="E1954" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1954" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G1954" t="inlineStr">
+        <is>
+          <t>SX235981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>11/9/26</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>Chadwicks</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>22502</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>BAUMIT PVC ANGLE (CORNER) BEAD WITH MESH 2.5M</t>
+        </is>
+      </c>
+      <c r="E1955" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1955" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G1955" t="inlineStr">
         <is>
           <t>SX235981</t>
         </is>
